--- a/Studymaterials/週間学習計画表生徒用_横型.xlsx
+++ b/Studymaterials/週間学習計画表生徒用_横型.xlsx
@@ -6,12 +6,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横型1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横型2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横型日曜始まり" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横型月曜始まり" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'横型1'!$A$1:$N$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'横型2'!$A$1:$N$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'横型日曜始まり'!$A$1:$N$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'横型月曜始まり'!$A$1:$N$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -56,16 +56,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -78,7 +84,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -119,6 +125,77 @@
     <border>
       <left/>
       <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal style="thin">
+        <color rgb="FF000000"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -215,47 +292,6 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalDown="1">
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal style="thin">
-        <color rgb="FF000000"/>
-      </diagonal>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -270,201 +306,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -475,59 +321,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -896,42 +729,42 @@
   <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="8" customWidth="1" style="12" min="1" max="1"/>
-    <col width="11.453125" customWidth="1" style="12" min="2" max="8"/>
-    <col width="1.453125" customWidth="1" style="12" min="9" max="9"/>
-    <col width="8.453125" customWidth="1" style="12" min="10" max="10"/>
-    <col width="10" customWidth="1" style="12" min="11" max="14"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11.453125" customWidth="1" min="2" max="8"/>
+    <col width="1.453125" customWidth="1" min="9" max="9"/>
+    <col width="8.453125" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="12">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>週間学習計画表（横型）</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="21" t="n"/>
-      <c r="H1" s="22" t="n"/>
+      <c r="B1" s="9" t="n"/>
+      <c r="C1" s="9" t="n"/>
+      <c r="D1" s="9" t="n"/>
+      <c r="E1" s="9" t="n"/>
+      <c r="F1" s="9" t="n"/>
+      <c r="G1" s="9" t="n"/>
+      <c r="H1" s="10" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="24" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="K1" s="24" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>教科別・補足</t>
         </is>
       </c>
-      <c r="L1" s="25" t="n"/>
-      <c r="M1" s="25" t="n"/>
-      <c r="N1" s="25" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="12">
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="10" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
@@ -941,67 +774,65 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-      <c r="J2" s="30" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>週目標</t>
         </is>
       </c>
-      <c r="K2" s="29" t="n"/>
-      <c r="L2" s="27" t="n"/>
-      <c r="M2" s="27" t="n"/>
-      <c r="N2" s="27" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" s="12">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="K2" s="13" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="17" t="n"/>
+      <c r="N2" s="18" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">         日付
 時間</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>月　日(日)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>月　日(月)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>月　日(火)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>月　日(水)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>月　日(木)</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>月　日(金)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>月　日(土)</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
-      <c r="L3" s="27" t="n"/>
-      <c r="M3" s="27" t="n"/>
-      <c r="N3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" s="12">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="20" t="n"/>
+      <c r="N3" s="21" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
@@ -1014,13 +845,11 @@
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="27" t="n"/>
-      <c r="M4" s="27" t="n"/>
-      <c r="N4" s="27" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="12">
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="20" t="n"/>
+      <c r="N4" s="21" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>0:00</t>
@@ -1034,13 +863,13 @@
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="2" t="n"/>
-      <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
-      <c r="L5" s="27" t="n"/>
-      <c r="M5" s="27" t="n"/>
-      <c r="N5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="12">
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="24" t="n"/>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="25" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>1:00</t>
@@ -1054,17 +883,17 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>英語</t>
         </is>
       </c>
-      <c r="K6" s="29" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" s="12">
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2:00</t>
@@ -1078,13 +907,11 @@
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="12">
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="N7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>3:00</t>
@@ -1098,13 +925,13 @@
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="2" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="12">
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="24" t="n"/>
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>4:00</t>
@@ -1118,17 +945,17 @@
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="2" t="n"/>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="12">
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>5:00</t>
@@ -1142,13 +969,11 @@
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="27" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="12">
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="N10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>6:00</t>
@@ -1162,13 +987,13 @@
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="12">
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="24" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="25" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>7:00</t>
@@ -1182,17 +1007,17 @@
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="2" t="n"/>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>国語</t>
         </is>
       </c>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="27" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" s="12">
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>8:00</t>
@@ -1206,13 +1031,11 @@
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="27" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" s="12">
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="N13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>9:00</t>
@@ -1226,13 +1049,13 @@
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" s="12">
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="24" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="25" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>10:00</t>
@@ -1246,17 +1069,17 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>理科</t>
         </is>
       </c>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="27" t="n"/>
-      <c r="N15" s="27" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" s="12">
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>11:00</t>
@@ -1270,13 +1093,11 @@
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="27" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" s="12">
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="N16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -1290,13 +1111,13 @@
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" s="12">
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="25" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>13:00</t>
@@ -1310,17 +1131,17 @@
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>社会</t>
         </is>
       </c>
-      <c r="K18" s="29" t="n"/>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="27" t="n"/>
-      <c r="N18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" s="12">
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>14:00</t>
@@ -1334,13 +1155,11 @@
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="2" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="27" t="n"/>
-      <c r="N19" s="27" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" s="12">
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="N19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>15:00</t>
@@ -1354,13 +1173,13 @@
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="12">
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="24" t="n"/>
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="25" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>16:00</t>
@@ -1374,17 +1193,17 @@
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>隙間</t>
         </is>
       </c>
-      <c r="K21" s="29" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="27" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" s="12">
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="17" t="n"/>
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>17:00</t>
@@ -1398,13 +1217,11 @@
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="27" t="n"/>
-      <c r="K22" s="27" t="n"/>
-      <c r="L22" s="27" t="n"/>
-      <c r="M22" s="27" t="n"/>
-      <c r="N22" s="27" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="12">
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="N22" s="21" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>18:00</t>
@@ -1418,13 +1235,13 @@
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="2" t="n"/>
-      <c r="J23" s="27" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="27" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="12">
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="24" t="n"/>
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="25" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>19:00</t>
@@ -1438,17 +1255,17 @@
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="2" t="n"/>
-      <c r="J24" s="30" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="27" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="12">
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="18" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>20:00</t>
@@ -1462,13 +1279,11 @@
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="2" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="12">
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="20" t="n"/>
+      <c r="N25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>21:00</t>
@@ -1482,13 +1297,11 @@
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="2" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="27" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="12">
+      <c r="J26" s="19" t="n"/>
+      <c r="K26" s="20" t="n"/>
+      <c r="N26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
@@ -1502,13 +1315,11 @@
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="27" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="27" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="12">
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="N27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>23:00</t>
@@ -1522,32 +1333,32 @@
       <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="2" t="n"/>
-      <c r="J28" s="27" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="27" t="n"/>
-      <c r="M28" s="27" t="n"/>
-      <c r="N28" s="27" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="24" t="n"/>
+      <c r="M28" s="24" t="n"/>
+      <c r="N28" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K9:N11"/>
+    <mergeCell ref="J12:J14"/>
     <mergeCell ref="J18:J20"/>
-    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="K12:N14"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="K6:N8"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K21:N23"/>
+    <mergeCell ref="K24:N28"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:N1"/>
     <mergeCell ref="K15:N17"/>
     <mergeCell ref="K2:N5"/>
     <mergeCell ref="K18:N20"/>
-    <mergeCell ref="K9:N11"/>
-    <mergeCell ref="K21:N23"/>
-    <mergeCell ref="K24:N28"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="K12:N14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
@@ -1564,42 +1375,42 @@
   <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="8" customWidth="1" style="12" min="1" max="1"/>
-    <col width="11.453125" customWidth="1" style="12" min="2" max="8"/>
-    <col width="1.453125" customWidth="1" style="12" min="9" max="9"/>
-    <col width="8.453125" customWidth="1" style="12" min="10" max="10"/>
-    <col width="10" customWidth="1" style="12" min="11" max="14"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11.453125" customWidth="1" min="2" max="8"/>
+    <col width="1.453125" customWidth="1" min="9" max="9"/>
+    <col width="8.453125" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="12">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>週間学習計画表（横型）</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="21" t="n"/>
-      <c r="H1" s="22" t="n"/>
+      <c r="B1" s="9" t="n"/>
+      <c r="C1" s="9" t="n"/>
+      <c r="D1" s="9" t="n"/>
+      <c r="E1" s="9" t="n"/>
+      <c r="F1" s="9" t="n"/>
+      <c r="G1" s="9" t="n"/>
+      <c r="H1" s="10" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="24" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="K1" s="24" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>教科別・補足</t>
         </is>
       </c>
-      <c r="L1" s="25" t="n"/>
-      <c r="M1" s="25" t="n"/>
-      <c r="N1" s="25" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="12">
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="10" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
@@ -1609,67 +1420,65 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-      <c r="J2" s="30" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>週目標</t>
         </is>
       </c>
-      <c r="K2" s="29" t="n"/>
-      <c r="L2" s="27" t="n"/>
-      <c r="M2" s="27" t="n"/>
-      <c r="N2" s="27" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" s="12">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="K2" s="13" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="17" t="n"/>
+      <c r="N2" s="18" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">         日付
 時間</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>月　日(月)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>月　日(火)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>月　日(水)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>月　日(木)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>月　日(金)</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>月　日(土)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>月　日(日)</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
-      <c r="L3" s="27" t="n"/>
-      <c r="M3" s="27" t="n"/>
-      <c r="N3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" s="12">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="20" t="n"/>
+      <c r="N3" s="21" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
@@ -1682,13 +1491,11 @@
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="27" t="n"/>
-      <c r="M4" s="27" t="n"/>
-      <c r="N4" s="27" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="12">
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="20" t="n"/>
+      <c r="N4" s="21" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>0:00</t>
@@ -1702,13 +1509,13 @@
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="2" t="n"/>
-      <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
-      <c r="L5" s="27" t="n"/>
-      <c r="M5" s="27" t="n"/>
-      <c r="N5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="12">
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="24" t="n"/>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="25" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>1:00</t>
@@ -1722,17 +1529,17 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>英語</t>
         </is>
       </c>
-      <c r="K6" s="29" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" s="12">
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2:00</t>
@@ -1746,13 +1553,11 @@
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="12">
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="N7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>3:00</t>
@@ -1766,13 +1571,13 @@
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="2" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="12">
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="24" t="n"/>
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>4:00</t>
@@ -1786,17 +1591,17 @@
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="2" t="n"/>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="12">
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>5:00</t>
@@ -1810,13 +1615,11 @@
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="27" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="12">
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="N10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>6:00</t>
@@ -1830,13 +1633,13 @@
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="12">
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="24" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="25" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>7:00</t>
@@ -1850,17 +1653,17 @@
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="2" t="n"/>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>国語</t>
         </is>
       </c>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="27" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" s="12">
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>8:00</t>
@@ -1874,13 +1677,11 @@
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="27" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" s="12">
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="N13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>9:00</t>
@@ -1894,13 +1695,13 @@
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" s="12">
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="24" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="25" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>10:00</t>
@@ -1914,17 +1715,17 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>理科</t>
         </is>
       </c>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="27" t="n"/>
-      <c r="N15" s="27" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" s="12">
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>11:00</t>
@@ -1938,13 +1739,11 @@
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="27" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" s="12">
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="N16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -1958,13 +1757,13 @@
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" s="12">
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="25" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>13:00</t>
@@ -1978,17 +1777,17 @@
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>社会</t>
         </is>
       </c>
-      <c r="K18" s="29" t="n"/>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="27" t="n"/>
-      <c r="N18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" s="12">
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>14:00</t>
@@ -2002,13 +1801,11 @@
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="2" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="27" t="n"/>
-      <c r="N19" s="27" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" s="12">
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="N19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>15:00</t>
@@ -2022,13 +1819,13 @@
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="12">
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="24" t="n"/>
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="25" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>16:00</t>
@@ -2042,17 +1839,17 @@
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>隙間</t>
         </is>
       </c>
-      <c r="K21" s="29" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="27" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" s="12">
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="17" t="n"/>
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>17:00</t>
@@ -2066,13 +1863,11 @@
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="27" t="n"/>
-      <c r="K22" s="27" t="n"/>
-      <c r="L22" s="27" t="n"/>
-      <c r="M22" s="27" t="n"/>
-      <c r="N22" s="27" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="12">
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="N22" s="21" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>18:00</t>
@@ -2086,13 +1881,13 @@
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="2" t="n"/>
-      <c r="J23" s="27" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="27" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="12">
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="24" t="n"/>
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="25" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>19:00</t>
@@ -2106,17 +1901,17 @@
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="2" t="n"/>
-      <c r="J24" s="30" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="27" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="12">
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="18" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>20:00</t>
@@ -2130,13 +1925,11 @@
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="2" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="12">
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="20" t="n"/>
+      <c r="N25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>21:00</t>
@@ -2150,13 +1943,11 @@
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="2" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="27" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="12">
+      <c r="J26" s="19" t="n"/>
+      <c r="K26" s="20" t="n"/>
+      <c r="N26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
@@ -2170,13 +1961,11 @@
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="27" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="27" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="12">
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="N27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>23:00</t>
@@ -2190,32 +1979,32 @@
       <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="2" t="n"/>
-      <c r="J28" s="27" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="27" t="n"/>
-      <c r="M28" s="27" t="n"/>
-      <c r="N28" s="27" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="24" t="n"/>
+      <c r="M28" s="24" t="n"/>
+      <c r="N28" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K9:N11"/>
+    <mergeCell ref="J12:J14"/>
     <mergeCell ref="J18:J20"/>
-    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="K12:N14"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="K6:N8"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K21:N23"/>
+    <mergeCell ref="K24:N28"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:N1"/>
     <mergeCell ref="K15:N17"/>
     <mergeCell ref="K2:N5"/>
     <mergeCell ref="K18:N20"/>
-    <mergeCell ref="K9:N11"/>
-    <mergeCell ref="K21:N23"/>
-    <mergeCell ref="K24:N28"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="K12:N14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>

--- a/Studymaterials/週間学習計画表生徒用_横型.xlsx
+++ b/Studymaterials/週間学習計画表生徒用_横型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakag\Desktop\GitHub\Myownproject\Studymaterials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEC8238-A527-4C7C-8C54-2910C37A3A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91716005-54AC-4F63-B5A6-593E4B6345DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="横型日曜始まり" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
-    <t>週間学習計画表（横型）</t>
-  </si>
-  <si>
     <t>項目</t>
   </si>
   <si>
@@ -158,6 +155,10 @@
   </si>
   <si>
     <t>23:00</t>
+  </si>
+  <si>
+    <t>週間学習計画表</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -458,14 +459,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -477,6 +470,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -793,26 +794,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="22"/>
       <c r="I1" s="7"/>
       <c r="J1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="13"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -825,48 +826,48 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="13"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="20"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -877,14 +878,14 @@
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="20"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -895,14 +896,14 @@
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="J5" s="10"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="23"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -913,16 +914,16 @@
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
       <c r="J6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="17"/>
+        <v>14</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="13"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -933,14 +934,14 @@
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -951,14 +952,14 @@
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="J8" s="10"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="23"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="19"/>
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -969,16 +970,16 @@
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>18</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="13"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -989,14 +990,14 @@
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="20"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1007,14 +1008,14 @@
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="10"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="23"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1025,16 +1026,16 @@
       <c r="H12" s="2"/>
       <c r="I12" s="1"/>
       <c r="J12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>22</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1045,14 +1046,14 @@
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1063,14 +1064,14 @@
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
       <c r="J14" s="10"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="23"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="19"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1081,16 +1082,16 @@
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>26</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="13"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1101,14 +1102,14 @@
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1119,14 +1120,14 @@
       <c r="H17" s="2"/>
       <c r="I17" s="1"/>
       <c r="J17" s="10"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="23"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="19"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1137,16 +1138,16 @@
       <c r="H18" s="2"/>
       <c r="I18" s="1"/>
       <c r="J18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1157,14 +1158,14 @@
       <c r="H19" s="2"/>
       <c r="I19" s="1"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="16"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1175,14 +1176,14 @@
       <c r="H20" s="2"/>
       <c r="I20" s="1"/>
       <c r="J20" s="10"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="23"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="19"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1193,16 +1194,16 @@
       <c r="H21" s="2"/>
       <c r="I21" s="1"/>
       <c r="J21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="13"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1213,14 +1214,14 @@
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="20"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="16"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1231,14 +1232,14 @@
       <c r="H23" s="2"/>
       <c r="I23" s="1"/>
       <c r="J23" s="10"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="23"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="19"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1249,16 +1250,16 @@
       <c r="H24" s="2"/>
       <c r="I24" s="1"/>
       <c r="J24" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>38</v>
+      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="13"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1269,14 +1270,14 @@
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="20"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="16"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1287,14 +1288,14 @@
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="9"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="20"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1305,14 +1306,14 @@
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1323,31 +1324,31 @@
       <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="23"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="K15:N17"/>
+    <mergeCell ref="K2:N5"/>
+    <mergeCell ref="K18:N20"/>
+    <mergeCell ref="K6:N8"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K9:N11"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J18:J20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="K12:N14"/>
     <mergeCell ref="J2:J5"/>
     <mergeCell ref="J24:J28"/>
     <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="K15:N17"/>
-    <mergeCell ref="K2:N5"/>
-    <mergeCell ref="K18:N20"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="K6:N8"/>
-    <mergeCell ref="J15:J17"/>
     <mergeCell ref="K21:N23"/>
     <mergeCell ref="K24:N28"/>
-    <mergeCell ref="K9:N11"/>
-    <mergeCell ref="J12:J14"/>
-    <mergeCell ref="J18:J20"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1372,26 +1373,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="22"/>
       <c r="I1" s="7"/>
       <c r="J1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="13"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -1404,48 +1405,48 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="13"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="20"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1456,14 +1457,14 @@
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="20"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1474,14 +1475,14 @@
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="J5" s="10"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="23"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1492,16 +1493,16 @@
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
       <c r="J6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="17"/>
+        <v>14</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="13"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1512,14 +1513,14 @@
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1530,14 +1531,14 @@
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="J8" s="10"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="23"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="19"/>
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1548,16 +1549,16 @@
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>18</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="13"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1568,14 +1569,14 @@
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="20"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1586,14 +1587,14 @@
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="10"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="23"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1604,16 +1605,16 @@
       <c r="H12" s="2"/>
       <c r="I12" s="1"/>
       <c r="J12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>22</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1624,14 +1625,14 @@
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1642,14 +1643,14 @@
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
       <c r="J14" s="10"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="23"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="19"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1660,16 +1661,16 @@
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>26</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="13"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1680,14 +1681,14 @@
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1698,14 +1699,14 @@
       <c r="H17" s="2"/>
       <c r="I17" s="1"/>
       <c r="J17" s="10"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="23"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="19"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1716,16 +1717,16 @@
       <c r="H18" s="2"/>
       <c r="I18" s="1"/>
       <c r="J18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1736,14 +1737,14 @@
       <c r="H19" s="2"/>
       <c r="I19" s="1"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="16"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1754,14 +1755,14 @@
       <c r="H20" s="2"/>
       <c r="I20" s="1"/>
       <c r="J20" s="10"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="23"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="19"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1772,16 +1773,16 @@
       <c r="H21" s="2"/>
       <c r="I21" s="1"/>
       <c r="J21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="13"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1792,14 +1793,14 @@
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="20"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="16"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1810,14 +1811,14 @@
       <c r="H23" s="2"/>
       <c r="I23" s="1"/>
       <c r="J23" s="10"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="23"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="19"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1828,16 +1829,16 @@
       <c r="H24" s="2"/>
       <c r="I24" s="1"/>
       <c r="J24" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>38</v>
+      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="13"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1848,14 +1849,14 @@
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="20"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="16"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1866,14 +1867,14 @@
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="9"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="20"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1884,14 +1885,14 @@
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1902,31 +1903,31 @@
       <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="23"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="K15:N17"/>
+    <mergeCell ref="K2:N5"/>
+    <mergeCell ref="K18:N20"/>
+    <mergeCell ref="K6:N8"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K9:N11"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J18:J20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="K12:N14"/>
     <mergeCell ref="J2:J5"/>
     <mergeCell ref="J24:J28"/>
     <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="K15:N17"/>
-    <mergeCell ref="K2:N5"/>
-    <mergeCell ref="K18:N20"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="K6:N8"/>
-    <mergeCell ref="J15:J17"/>
     <mergeCell ref="K21:N23"/>
     <mergeCell ref="K24:N28"/>
-    <mergeCell ref="K9:N11"/>
-    <mergeCell ref="J12:J14"/>
-    <mergeCell ref="J18:J20"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
